--- a/data/case/output/品質分析.xlsx
+++ b/data/case/output/品質分析.xlsx
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46306.38184027778</v>
+        <v>46306.38690972222</v>
       </c>
     </row>
     <row r="4">
